--- a/Assets/Data/DataTable/01_Character_Table_fix.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB68251-8D9E-4DC8-A130-0FE9EFA42B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36FF0BA-ECE6-4C6E-AF54-6E831869A9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -483,6 +483,276 @@
         </r>
       </text>
     </comment>
+    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{A3CC39BE-B40B-4ADE-9373-072C91593446}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">물리
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">화염
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">3: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">방사능
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">4: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">중력
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">5: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">공허
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">6: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>신성</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R3" authorId="0" shapeId="0" xr:uid="{8FE4A925-8291-466B-98E1-E41BD960CA85}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">물리
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">화염
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">3: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">방사능
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">4: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">중력
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">5: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">공허
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">6: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>신성</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -850,10 +1120,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>속성 게이지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>속성 게이지 저항 계수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -963,6 +1229,10 @@
   </si>
   <si>
     <t>Monster_Name_2004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>속성 게이지 효율 계수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3963,16 +4233,16 @@
         <v>93</v>
       </c>
       <c r="P2" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q2" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="Q2" s="22" t="s">
+      <c r="R2" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="R2" s="22" t="s">
+      <c r="S2" s="22" t="s">
         <v>96</v>
-      </c>
-      <c r="S2" s="22" t="s">
-        <v>97</v>
       </c>
       <c r="T2" s="22"/>
       <c r="U2" s="22"/>
@@ -4024,16 +4294,16 @@
         <v>84</v>
       </c>
       <c r="O3" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="P3" s="29" t="s">
         <v>98</v>
-      </c>
-      <c r="P3" s="29" t="s">
-        <v>99</v>
       </c>
       <c r="Q3" s="29" t="s">
         <v>84</v>
       </c>
       <c r="R3" s="29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="S3" s="29" t="s">
         <v>70</v>
@@ -4058,49 +4328,49 @@
         <v>63</v>
       </c>
       <c r="E4" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>111</v>
-      </c>
       <c r="G4" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="L4" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="I4" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="K4" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="L4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="P4" s="26" t="s">
+      <c r="Q4" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="Q4" s="26" t="s">
+      <c r="R4" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="R4" s="26" t="s">
+      <c r="S4" s="26" t="s">
         <v>108</v>
-      </c>
-      <c r="S4" s="26" t="s">
-        <v>109</v>
       </c>
       <c r="T4" s="26"/>
       <c r="U4" s="26"/>
@@ -4123,7 +4393,7 @@
         <v>1001</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F5" s="34">
         <v>100</v>
@@ -4153,19 +4423,19 @@
         <v>1.3</v>
       </c>
       <c r="O5" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="P5" s="33" t="s">
         <v>112</v>
-      </c>
-      <c r="P5" s="33" t="s">
-        <v>113</v>
       </c>
       <c r="Q5" s="34">
         <v>1</v>
       </c>
       <c r="R5" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="S5" s="25" t="s">
         <v>113</v>
-      </c>
-      <c r="S5" s="25" t="s">
-        <v>114</v>
       </c>
       <c r="T5" s="25"/>
       <c r="U5" s="25"/>
@@ -4188,7 +4458,7 @@
         <v>1002</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F6" s="34">
         <v>100</v>
@@ -4222,7 +4492,7 @@
       <c r="Q6" s="24"/>
       <c r="R6" s="33"/>
       <c r="S6" s="25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T6" s="25"/>
       <c r="U6" s="25"/>
@@ -4245,7 +4515,7 @@
         <v>1003</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F7" s="34">
         <v>100</v>
@@ -4279,7 +4549,7 @@
       <c r="Q7" s="24"/>
       <c r="R7" s="33"/>
       <c r="S7" s="33" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T7" s="33"/>
       <c r="U7" s="33"/>
@@ -4302,7 +4572,7 @@
         <v>2001</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F8" s="34">
         <v>100</v>
@@ -4336,7 +4606,7 @@
       <c r="Q8" s="24"/>
       <c r="R8" s="33"/>
       <c r="S8" s="33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="T8" s="33"/>
       <c r="U8" s="33"/>
@@ -4359,7 +4629,7 @@
         <v>2002</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F9" s="34">
         <v>100</v>
@@ -4393,7 +4663,7 @@
       <c r="Q9" s="24"/>
       <c r="R9" s="33"/>
       <c r="S9" s="33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="T9" s="33"/>
       <c r="U9" s="33"/>
@@ -4416,7 +4686,7 @@
         <v>2003</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F10" s="34">
         <v>100</v>
@@ -4450,7 +4720,7 @@
       <c r="Q10" s="24"/>
       <c r="R10" s="33"/>
       <c r="S10" s="33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="T10" s="33"/>
       <c r="U10" s="33"/>
@@ -4473,7 +4743,7 @@
         <v>2004</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F11" s="34">
         <v>100</v>
@@ -4507,7 +4777,7 @@
       <c r="Q11" s="24"/>
       <c r="R11" s="33"/>
       <c r="S11" s="33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T11" s="33"/>
       <c r="U11" s="33"/>

--- a/Assets/Data/DataTable/01_Character_Table_fix.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table_fix.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36FF0BA-ECE6-4C6E-AF54-6E831869A9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10AC687-B13C-4102-8622-F368AC6B2DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -345,6 +345,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>전세혁</author>
+    <author>제동우</author>
   </authors>
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{4E6B084F-FA63-4203-8F0E-6D0C0A5F7A83}">
@@ -483,7 +484,23 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{A3CC39BE-B40B-4ADE-9373-072C91593446}">
+    <comment ref="E3" authorId="1" shapeId="0" xr:uid="{F78C218E-950D-4350-B202-6F0ACDE87E56}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>0: NONE
+1: Player
+2: Enemy</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{A3CC39BE-B40B-4ADE-9373-072C91593446}">
       <text>
         <r>
           <rPr>
@@ -618,7 +635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="0" shapeId="0" xr:uid="{8FE4A925-8291-466B-98E1-E41BD960CA85}">
+    <comment ref="S3" authorId="0" shapeId="0" xr:uid="{8FE4A925-8291-466B-98E1-E41BD960CA85}">
       <text>
         <r>
           <rPr>
@@ -758,7 +775,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="133">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1233,6 +1250,21 @@
   </si>
   <si>
     <t>속성 게이지 효율 계수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum:SIDE:NONE</t>
+  </si>
+  <si>
+    <t>enum:SIDE:NONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐릭터 진영 구분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Char_SIDE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3705,6 +3737,9 @@
   </sheetPr>
   <dimension ref="A2:E18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -3799,6 +3834,9 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
+        <v>130</v>
+      </c>
       <c r="C13" t="s">
         <v>72</v>
       </c>
@@ -4155,38 +4193,39 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.375" style="32" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.875" style="31" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="28" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>81</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>77</v>
       </c>
@@ -4199,58 +4238,61 @@
       <c r="D2" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="F2" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="G2" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="H2" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="I2" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="J2" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="K2" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="L2" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="L2" s="22" t="s">
+      <c r="M2" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="M2" s="22" t="s">
+      <c r="N2" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="N2" s="22" t="s">
+      <c r="O2" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="P2" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="P2" s="22" t="s">
+      <c r="Q2" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q2" s="22" t="s">
+      <c r="R2" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="R2" s="22" t="s">
+      <c r="S2" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="S2" s="22" t="s">
+      <c r="T2" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="T2" s="22"/>
       <c r="U2" s="22"/>
       <c r="V2" s="22"/>
       <c r="W2" s="22"/>
       <c r="X2" s="22"/>
+      <c r="Y2" s="22"/>
     </row>
-    <row r="3" spans="1:24" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
         <v>58</v>
       </c>
@@ -4264,25 +4306,25 @@
         <v>58</v>
       </c>
       <c r="E3" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="G3" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="H3" s="29" t="s">
         <v>58</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>84</v>
       </c>
       <c r="I3" s="29" t="s">
         <v>84</v>
       </c>
       <c r="J3" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" s="29" t="s">
         <v>58</v>
-      </c>
-      <c r="K3" s="29" t="s">
-        <v>84</v>
       </c>
       <c r="L3" s="29" t="s">
         <v>84</v>
@@ -4294,27 +4336,30 @@
         <v>84</v>
       </c>
       <c r="O3" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="P3" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="P3" s="29" t="s">
+      <c r="Q3" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="Q3" s="29" t="s">
+      <c r="R3" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="R3" s="29" t="s">
+      <c r="S3" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="S3" s="29" t="s">
+      <c r="T3" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="T3" s="29"/>
       <c r="U3" s="29"/>
       <c r="V3" s="29"/>
       <c r="W3" s="29"/>
       <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
     </row>
-    <row r="4" spans="1:24" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>55</v>
       </c>
@@ -4328,57 +4373,60 @@
         <v>63</v>
       </c>
       <c r="E4" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="P4" s="26" t="s">
+      <c r="Q4" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="Q4" s="26" t="s">
+      <c r="R4" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="R4" s="26" t="s">
+      <c r="S4" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="S4" s="26" t="s">
+      <c r="T4" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="26"/>
       <c r="U4" s="26"/>
       <c r="V4" s="26"/>
       <c r="W4" s="26"/>
       <c r="X4" s="26"/>
+      <c r="Y4" s="26"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="24">
         <f>(B5*1000000) + (C5*10000) + D5</f>
         <v>10001001</v>
@@ -4392,58 +4440,61 @@
       <c r="D5" s="24">
         <v>1001</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="24">
+        <v>1</v>
+      </c>
+      <c r="F5" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="F5" s="34">
+      <c r="G5" s="34">
         <v>100</v>
       </c>
-      <c r="G5" s="24">
+      <c r="H5" s="24">
         <v>9</v>
       </c>
-      <c r="H5" s="34">
+      <c r="I5" s="34">
         <v>40</v>
       </c>
-      <c r="I5" s="34">
+      <c r="J5" s="34">
         <v>10</v>
       </c>
-      <c r="J5" s="24">
+      <c r="K5" s="24">
         <v>3</v>
       </c>
-      <c r="K5" s="24">
+      <c r="L5" s="24">
         <v>10</v>
       </c>
-      <c r="L5" s="34">
+      <c r="M5" s="34">
         <v>0.3</v>
-      </c>
-      <c r="M5" s="34">
-        <v>1.3</v>
       </c>
       <c r="N5" s="34">
         <v>1.3</v>
       </c>
-      <c r="O5" s="33" t="s">
+      <c r="O5" s="34">
+        <v>1.3</v>
+      </c>
+      <c r="P5" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="P5" s="33" t="s">
+      <c r="Q5" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="Q5" s="34">
+      <c r="R5" s="34">
         <v>1</v>
       </c>
-      <c r="R5" s="33" t="s">
+      <c r="S5" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="S5" s="25" t="s">
+      <c r="T5" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="T5" s="25"/>
       <c r="U5" s="25"/>
       <c r="V5" s="25"/>
       <c r="W5" s="25"/>
       <c r="X5" s="25"/>
+      <c r="Y5" s="25"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="24">
         <f>(B6*1000000) + (C6*100000) + D6</f>
         <v>10001002</v>
@@ -4457,50 +4508,53 @@
       <c r="D6" s="24">
         <v>1002</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="24">
+        <v>1</v>
+      </c>
+      <c r="F6" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="F6" s="34">
+      <c r="G6" s="34">
         <v>100</v>
       </c>
-      <c r="G6" s="24">
+      <c r="H6" s="24">
         <v>9</v>
       </c>
-      <c r="H6" s="34">
+      <c r="I6" s="34">
         <v>40</v>
       </c>
-      <c r="I6" s="34">
+      <c r="J6" s="34">
         <v>10</v>
       </c>
-      <c r="J6" s="24">
+      <c r="K6" s="24">
         <v>3</v>
       </c>
-      <c r="K6" s="24">
+      <c r="L6" s="24">
         <v>10</v>
       </c>
-      <c r="L6" s="34">
+      <c r="M6" s="34">
         <v>0.3</v>
-      </c>
-      <c r="M6" s="34">
-        <v>1.3</v>
       </c>
       <c r="N6" s="34">
         <v>1.3</v>
       </c>
-      <c r="O6" s="33"/>
+      <c r="O6" s="34">
+        <v>1.3</v>
+      </c>
       <c r="P6" s="33"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="33"/>
-      <c r="S6" s="25" t="s">
+      <c r="Q6" s="33"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="33"/>
+      <c r="T6" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="T6" s="25"/>
       <c r="U6" s="25"/>
       <c r="V6" s="25"/>
       <c r="W6" s="25"/>
       <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="24">
         <f t="shared" ref="A7" si="0">(B7*1000000) + (C7*10000) + D7</f>
         <v>10001003</v>
@@ -4514,50 +4568,53 @@
       <c r="D7" s="24">
         <v>1003</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="24">
+        <v>1</v>
+      </c>
+      <c r="F7" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="F7" s="34">
+      <c r="G7" s="34">
         <v>100</v>
       </c>
-      <c r="G7" s="24">
+      <c r="H7" s="24">
         <v>9</v>
       </c>
-      <c r="H7" s="34">
+      <c r="I7" s="34">
         <v>40</v>
       </c>
-      <c r="I7" s="34">
+      <c r="J7" s="34">
         <v>10</v>
       </c>
-      <c r="J7" s="24">
+      <c r="K7" s="24">
         <v>3</v>
       </c>
-      <c r="K7" s="24">
+      <c r="L7" s="24">
         <v>10</v>
       </c>
-      <c r="L7" s="34">
+      <c r="M7" s="34">
         <v>0.3</v>
-      </c>
-      <c r="M7" s="34">
-        <v>1.3</v>
       </c>
       <c r="N7" s="34">
         <v>1.3</v>
       </c>
-      <c r="O7" s="33"/>
+      <c r="O7" s="34">
+        <v>1.3</v>
+      </c>
       <c r="P7" s="33"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="33"/>
-      <c r="S7" s="33" t="s">
+      <c r="Q7" s="33"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="33"/>
+      <c r="T7" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="T7" s="33"/>
       <c r="U7" s="33"/>
       <c r="V7" s="33"/>
       <c r="W7" s="33"/>
       <c r="X7" s="33"/>
+      <c r="Y7" s="33"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="24">
         <f t="shared" ref="A8" si="1">(B8*1000000) + (C8*100000) + D8</f>
         <v>10102001</v>
@@ -4571,50 +4628,53 @@
       <c r="D8" s="24">
         <v>2001</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="24">
+        <v>2</v>
+      </c>
+      <c r="F8" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F8" s="34">
+      <c r="G8" s="34">
         <v>100</v>
       </c>
-      <c r="G8" s="24">
+      <c r="H8" s="24">
         <v>9</v>
       </c>
-      <c r="H8" s="34">
+      <c r="I8" s="34">
         <v>40</v>
       </c>
-      <c r="I8" s="34">
+      <c r="J8" s="34">
         <v>10</v>
       </c>
-      <c r="J8" s="24">
+      <c r="K8" s="24">
         <v>3</v>
       </c>
-      <c r="K8" s="24">
+      <c r="L8" s="24">
         <v>10</v>
       </c>
-      <c r="L8" s="34">
+      <c r="M8" s="34">
         <v>0.3</v>
       </c>
-      <c r="M8" s="34">
+      <c r="N8" s="34">
         <v>1.3</v>
       </c>
-      <c r="N8" s="34">
+      <c r="O8" s="34">
         <v>1</v>
       </c>
-      <c r="O8" s="33"/>
       <c r="P8" s="33"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33" t="s">
+      <c r="Q8" s="33"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="33"/>
+      <c r="T8" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="T8" s="33"/>
       <c r="U8" s="33"/>
       <c r="V8" s="33"/>
       <c r="W8" s="33"/>
       <c r="X8" s="33"/>
+      <c r="Y8" s="33"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="24">
         <f t="shared" ref="A9" si="2">(B9*1000000) + (C9*10000) + D9</f>
         <v>10012002</v>
@@ -4628,50 +4688,53 @@
       <c r="D9" s="24">
         <v>2002</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="24">
+        <v>2</v>
+      </c>
+      <c r="F9" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="F9" s="34">
+      <c r="G9" s="34">
         <v>100</v>
       </c>
-      <c r="G9" s="24">
+      <c r="H9" s="24">
         <v>9</v>
       </c>
-      <c r="H9" s="34">
+      <c r="I9" s="34">
         <v>40</v>
       </c>
-      <c r="I9" s="34">
+      <c r="J9" s="34">
         <v>10</v>
       </c>
-      <c r="J9" s="24">
+      <c r="K9" s="24">
         <v>3</v>
       </c>
-      <c r="K9" s="24">
+      <c r="L9" s="24">
         <v>10</v>
       </c>
-      <c r="L9" s="34">
+      <c r="M9" s="34">
         <v>0.3</v>
       </c>
-      <c r="M9" s="34">
+      <c r="N9" s="34">
         <v>1.3</v>
       </c>
-      <c r="N9" s="34">
+      <c r="O9" s="34">
         <v>1</v>
       </c>
-      <c r="O9" s="33"/>
       <c r="P9" s="33"/>
-      <c r="Q9" s="24"/>
-      <c r="R9" s="33"/>
-      <c r="S9" s="33" t="s">
+      <c r="Q9" s="33"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="33"/>
+      <c r="T9" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="T9" s="33"/>
       <c r="U9" s="33"/>
       <c r="V9" s="33"/>
       <c r="W9" s="33"/>
       <c r="X9" s="33"/>
+      <c r="Y9" s="33"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="24">
         <f t="shared" ref="A10" si="3">(B10*1000000) + (C10*100000) + D10</f>
         <v>10102003</v>
@@ -4685,50 +4748,53 @@
       <c r="D10" s="24">
         <v>2003</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="E10" s="24">
+        <v>2</v>
+      </c>
+      <c r="F10" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="F10" s="34">
+      <c r="G10" s="34">
         <v>100</v>
       </c>
-      <c r="G10" s="24">
+      <c r="H10" s="24">
         <v>9</v>
       </c>
-      <c r="H10" s="34">
+      <c r="I10" s="34">
         <v>40</v>
       </c>
-      <c r="I10" s="34">
+      <c r="J10" s="34">
         <v>10</v>
       </c>
-      <c r="J10" s="24">
+      <c r="K10" s="24">
         <v>3</v>
       </c>
-      <c r="K10" s="24">
+      <c r="L10" s="24">
         <v>10</v>
       </c>
-      <c r="L10" s="34">
+      <c r="M10" s="34">
         <v>0.3</v>
       </c>
-      <c r="M10" s="34">
+      <c r="N10" s="34">
         <v>1.3</v>
       </c>
-      <c r="N10" s="34">
+      <c r="O10" s="34">
         <v>1</v>
       </c>
-      <c r="O10" s="33"/>
       <c r="P10" s="33"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33" t="s">
+      <c r="Q10" s="33"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="T10" s="33"/>
       <c r="U10" s="33"/>
       <c r="V10" s="33"/>
       <c r="W10" s="33"/>
       <c r="X10" s="33"/>
+      <c r="Y10" s="33"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="24">
         <f t="shared" ref="A11" si="4">(B11*1000000) + (C11*10000) + D11</f>
         <v>10012004</v>
@@ -4742,178 +4808,186 @@
       <c r="D11" s="24">
         <v>2004</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="24">
+        <v>2</v>
+      </c>
+      <c r="F11" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="F11" s="34">
+      <c r="G11" s="34">
         <v>100</v>
       </c>
-      <c r="G11" s="24">
+      <c r="H11" s="24">
         <v>9</v>
       </c>
-      <c r="H11" s="34">
+      <c r="I11" s="34">
         <v>40</v>
       </c>
-      <c r="I11" s="34">
+      <c r="J11" s="34">
         <v>10</v>
       </c>
-      <c r="J11" s="24">
+      <c r="K11" s="24">
         <v>3</v>
       </c>
-      <c r="K11" s="24">
+      <c r="L11" s="24">
         <v>10</v>
       </c>
-      <c r="L11" s="34">
+      <c r="M11" s="34">
         <v>0.3</v>
       </c>
-      <c r="M11" s="34">
+      <c r="N11" s="34">
         <v>1.3</v>
       </c>
-      <c r="N11" s="34">
+      <c r="O11" s="34">
         <v>1</v>
       </c>
-      <c r="O11" s="33"/>
       <c r="P11" s="33"/>
-      <c r="Q11" s="24"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="33" t="s">
+      <c r="Q11" s="33"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="T11" s="33"/>
       <c r="U11" s="33"/>
       <c r="V11" s="33"/>
       <c r="W11" s="33"/>
       <c r="X11" s="33"/>
+      <c r="Y11" s="33"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="24"/>
       <c r="B12" s="35"/>
       <c r="C12" s="30"/>
       <c r="D12" s="24"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="34"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="24"/>
       <c r="I12" s="34"/>
-      <c r="J12" s="24"/>
+      <c r="J12" s="34"/>
       <c r="K12" s="24"/>
-      <c r="L12" s="34"/>
+      <c r="L12" s="24"/>
       <c r="M12" s="34"/>
       <c r="N12" s="34"/>
-      <c r="O12" s="33"/>
+      <c r="O12" s="34"/>
       <c r="P12" s="33"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="33"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="24"/>
       <c r="S12" s="33"/>
       <c r="T12" s="33"/>
       <c r="U12" s="33"/>
       <c r="V12" s="33"/>
       <c r="W12" s="33"/>
       <c r="X12" s="33"/>
+      <c r="Y12" s="33"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="24"/>
       <c r="B13" s="35"/>
       <c r="C13" s="30"/>
       <c r="D13" s="33"/>
       <c r="E13" s="33"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="34"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="24"/>
       <c r="I13" s="34"/>
-      <c r="J13" s="24"/>
+      <c r="J13" s="34"/>
       <c r="K13" s="24"/>
-      <c r="L13" s="34"/>
+      <c r="L13" s="24"/>
       <c r="M13" s="34"/>
       <c r="N13" s="34"/>
-      <c r="O13" s="33"/>
+      <c r="O13" s="34"/>
       <c r="P13" s="33"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="33"/>
+      <c r="Q13" s="33"/>
+      <c r="R13" s="24"/>
       <c r="S13" s="33"/>
       <c r="T13" s="33"/>
       <c r="U13" s="33"/>
       <c r="V13" s="33"/>
       <c r="W13" s="33"/>
       <c r="X13" s="33"/>
+      <c r="Y13" s="33"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="24"/>
       <c r="B14" s="35"/>
       <c r="C14" s="30"/>
       <c r="D14" s="33"/>
       <c r="E14" s="33"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="34"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="24"/>
       <c r="I14" s="34"/>
-      <c r="J14" s="24"/>
+      <c r="J14" s="34"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="34"/>
+      <c r="L14" s="24"/>
       <c r="M14" s="34"/>
       <c r="N14" s="34"/>
-      <c r="O14" s="33"/>
+      <c r="O14" s="34"/>
       <c r="P14" s="33"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="33"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="24"/>
       <c r="S14" s="33"/>
       <c r="T14" s="33"/>
       <c r="U14" s="33"/>
       <c r="V14" s="33"/>
       <c r="W14" s="33"/>
       <c r="X14" s="33"/>
+      <c r="Y14" s="33"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="24"/>
       <c r="B15" s="35"/>
       <c r="C15" s="30"/>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="34"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="24"/>
       <c r="I15" s="34"/>
-      <c r="J15" s="24"/>
+      <c r="J15" s="34"/>
       <c r="K15" s="24"/>
-      <c r="L15" s="34"/>
+      <c r="L15" s="24"/>
       <c r="M15" s="34"/>
       <c r="N15" s="34"/>
-      <c r="O15" s="33"/>
+      <c r="O15" s="34"/>
       <c r="P15" s="33"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="33"/>
+      <c r="Q15" s="33"/>
+      <c r="R15" s="24"/>
       <c r="S15" s="33"/>
       <c r="T15" s="33"/>
       <c r="U15" s="33"/>
       <c r="V15" s="33"/>
       <c r="W15" s="33"/>
       <c r="X15" s="33"/>
+      <c r="Y15" s="33"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="33"/>
       <c r="B16" s="24"/>
       <c r="C16" s="30"/>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="34"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="24"/>
       <c r="I16" s="34"/>
-      <c r="J16" s="24"/>
+      <c r="J16" s="34"/>
       <c r="K16" s="24"/>
-      <c r="L16" s="34"/>
+      <c r="L16" s="24"/>
       <c r="M16" s="34"/>
       <c r="N16" s="34"/>
-      <c r="O16" s="33"/>
+      <c r="O16" s="34"/>
       <c r="P16" s="33"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="33"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="24"/>
       <c r="S16" s="33"/>
       <c r="T16" s="33"/>
       <c r="U16" s="33"/>
       <c r="V16" s="33"/>
       <c r="W16" s="33"/>
       <c r="X16" s="33"/>
+      <c r="Y16" s="33"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4921,12 +4995,12 @@
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D44D287-4A0D-4E30-B02E-F978C229F037}">
           <x14:formula1>
             <xm:f>'!Logic'!$A$5:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>A3:K3</xm:sqref>
+          <xm:sqref>A3:L3</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Assets/Data/DataTable/01_Character_Table_fix.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10AC687-B13C-4102-8622-F368AC6B2DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F28103-719E-4983-9038-5F29ED932785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1155,12 +1155,6 @@
     <t>double[]</t>
   </si>
   <si>
-    <t>Char_Default_SP</t>
-  </si>
-  <si>
-    <t>Char_Default_Speed</t>
-  </si>
-  <si>
     <t>Critical_Chance</t>
   </si>
   <si>
@@ -1185,12 +1179,6 @@
     <t>Asset_File</t>
   </si>
   <si>
-    <t>Char_Name</t>
-  </si>
-  <si>
-    <t>Char_Max_HP</t>
-  </si>
-  <si>
     <t>20010001,20010002,20010003</t>
   </si>
   <si>
@@ -1218,9 +1206,6 @@
     <t>penguin_Berserker</t>
   </si>
   <si>
-    <t>Char_Default_Defense</t>
-  </si>
-  <si>
     <t>Character_Name_1001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1264,7 +1249,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Char_SIDE</t>
+    <t>SIDE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max_HP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default_SP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default_Speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default_Defense</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1272,9 +1277,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="177" formatCode="00"/>
     <numFmt numFmtId="178" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
@@ -1431,7 +1435,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1522,22 +1526,16 @@
     <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3835,7 +3833,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C13" t="s">
         <v>72</v>
@@ -4196,10 +4194,10 @@
   <dimension ref="A1:Y16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.375" style="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.875" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.375" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.875" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.125" style="33" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.375" bestFit="1" customWidth="1"/>
@@ -4224,6 +4222,7 @@
       </c>
       <c r="B1"/>
       <c r="C1"/>
+      <c r="D1"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
@@ -4239,7 +4238,7 @@
         <v>76</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>82</v>
@@ -4275,7 +4274,7 @@
         <v>93</v>
       </c>
       <c r="Q2" s="22" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="R2" s="22" t="s">
         <v>94</v>
@@ -4294,19 +4293,19 @@
     </row>
     <row r="3" spans="1:25" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F3" s="29" t="s">
         <v>70</v>
@@ -4373,52 +4372,52 @@
         <v>63</v>
       </c>
       <c r="E4" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="J4" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="H4" s="26" t="s">
+      <c r="K4" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="M4" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="K4" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="M4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="Q4" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="P4" s="26" t="s">
+      <c r="R4" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="Q4" s="26" t="s">
+      <c r="S4" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="R4" s="26" t="s">
+      <c r="T4" s="26" t="s">
         <v>106</v>
-      </c>
-      <c r="S4" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="T4" s="26" t="s">
-        <v>108</v>
       </c>
       <c r="U4" s="26"/>
       <c r="V4" s="26"/>
@@ -4427,35 +4426,35 @@
       <c r="Y4" s="26"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A5" s="24">
+      <c r="A5" s="25">
         <f>(B5*1000000) + (C5*10000) + D5</f>
         <v>10001001</v>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="32">
         <v>10</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="25">
         <v>0</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>1001</v>
       </c>
       <c r="E5" s="24">
         <v>1</v>
       </c>
-      <c r="F5" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="G5" s="34">
+      <c r="F5" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="G5" s="31">
         <v>100</v>
       </c>
       <c r="H5" s="24">
         <v>9</v>
       </c>
-      <c r="I5" s="34">
+      <c r="I5" s="31">
         <v>40</v>
       </c>
-      <c r="J5" s="34">
+      <c r="J5" s="31">
         <v>10</v>
       </c>
       <c r="K5" s="24">
@@ -4464,29 +4463,29 @@
       <c r="L5" s="24">
         <v>10</v>
       </c>
-      <c r="M5" s="34">
+      <c r="M5" s="31">
         <v>0.3</v>
       </c>
-      <c r="N5" s="34">
+      <c r="N5" s="31">
         <v>1.3</v>
       </c>
-      <c r="O5" s="34">
+      <c r="O5" s="31">
         <v>1.3</v>
       </c>
-      <c r="P5" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q5" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="R5" s="34">
+      <c r="P5" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q5" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="R5" s="31">
         <v>1</v>
       </c>
-      <c r="S5" s="33" t="s">
-        <v>112</v>
+      <c r="S5" s="30" t="s">
+        <v>108</v>
       </c>
       <c r="T5" s="25" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="U5" s="25"/>
       <c r="V5" s="25"/>
@@ -4495,35 +4494,35 @@
       <c r="Y5" s="25"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A6" s="24">
+      <c r="A6" s="25">
         <f>(B6*1000000) + (C6*100000) + D6</f>
         <v>10001002</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="32">
         <v>10</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>0</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>1002</v>
       </c>
       <c r="E6" s="24">
         <v>1</v>
       </c>
-      <c r="F6" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="G6" s="34">
+      <c r="F6" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="G6" s="31">
         <v>100</v>
       </c>
       <c r="H6" s="24">
         <v>9</v>
       </c>
-      <c r="I6" s="34">
+      <c r="I6" s="31">
         <v>40</v>
       </c>
-      <c r="J6" s="34">
+      <c r="J6" s="31">
         <v>10</v>
       </c>
       <c r="K6" s="24">
@@ -4532,21 +4531,21 @@
       <c r="L6" s="24">
         <v>10</v>
       </c>
-      <c r="M6" s="34">
+      <c r="M6" s="31">
         <v>0.3</v>
       </c>
-      <c r="N6" s="34">
+      <c r="N6" s="31">
         <v>1.3</v>
       </c>
-      <c r="O6" s="34">
+      <c r="O6" s="31">
         <v>1.3</v>
       </c>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="30"/>
       <c r="R6" s="24"/>
-      <c r="S6" s="33"/>
+      <c r="S6" s="30"/>
       <c r="T6" s="25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="U6" s="25"/>
       <c r="V6" s="25"/>
@@ -4555,35 +4554,35 @@
       <c r="Y6" s="25"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A7" s="24">
+      <c r="A7" s="25">
         <f t="shared" ref="A7" si="0">(B7*1000000) + (C7*10000) + D7</f>
         <v>10001003</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="33">
         <v>10</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="25">
         <v>0</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>1003</v>
       </c>
       <c r="E7" s="24">
         <v>1</v>
       </c>
-      <c r="F7" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="G7" s="34">
+      <c r="F7" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="G7" s="31">
         <v>100</v>
       </c>
       <c r="H7" s="24">
         <v>9</v>
       </c>
-      <c r="I7" s="34">
+      <c r="I7" s="31">
         <v>40</v>
       </c>
-      <c r="J7" s="34">
+      <c r="J7" s="31">
         <v>10</v>
       </c>
       <c r="K7" s="24">
@@ -4592,58 +4591,58 @@
       <c r="L7" s="24">
         <v>10</v>
       </c>
-      <c r="M7" s="34">
+      <c r="M7" s="31">
         <v>0.3</v>
       </c>
-      <c r="N7" s="34">
+      <c r="N7" s="31">
         <v>1.3</v>
       </c>
-      <c r="O7" s="34">
+      <c r="O7" s="31">
         <v>1.3</v>
       </c>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
       <c r="R7" s="24"/>
-      <c r="S7" s="33"/>
-      <c r="T7" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="U7" s="33"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="33"/>
-      <c r="Y7" s="33"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="U7" s="30"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="30"/>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A8" s="24">
+      <c r="A8" s="25">
         <f t="shared" ref="A8" si="1">(B8*1000000) + (C8*100000) + D8</f>
         <v>10102001</v>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="32">
         <v>10</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="25">
         <v>1</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>2001</v>
       </c>
       <c r="E8" s="24">
         <v>2</v>
       </c>
-      <c r="F8" s="33" t="s">
-        <v>124</v>
-      </c>
-      <c r="G8" s="34">
+      <c r="F8" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="G8" s="31">
         <v>100</v>
       </c>
       <c r="H8" s="24">
         <v>9</v>
       </c>
-      <c r="I8" s="34">
+      <c r="I8" s="31">
         <v>40</v>
       </c>
-      <c r="J8" s="34">
+      <c r="J8" s="31">
         <v>10</v>
       </c>
       <c r="K8" s="24">
@@ -4652,58 +4651,58 @@
       <c r="L8" s="24">
         <v>10</v>
       </c>
-      <c r="M8" s="34">
+      <c r="M8" s="31">
         <v>0.3</v>
       </c>
-      <c r="N8" s="34">
+      <c r="N8" s="31">
         <v>1.3</v>
       </c>
-      <c r="O8" s="34">
+      <c r="O8" s="31">
         <v>1</v>
       </c>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="30"/>
       <c r="R8" s="24"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33" t="s">
-        <v>116</v>
-      </c>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="33"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="U8" s="30"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="30"/>
+      <c r="Y8" s="30"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A9" s="24">
+      <c r="A9" s="25">
         <f t="shared" ref="A9" si="2">(B9*1000000) + (C9*10000) + D9</f>
         <v>10012002</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="32">
         <v>10</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="25">
         <v>1</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>2002</v>
       </c>
       <c r="E9" s="24">
         <v>2</v>
       </c>
-      <c r="F9" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="G9" s="34">
+      <c r="F9" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" s="31">
         <v>100</v>
       </c>
       <c r="H9" s="24">
         <v>9</v>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="31">
         <v>40</v>
       </c>
-      <c r="J9" s="34">
+      <c r="J9" s="31">
         <v>10</v>
       </c>
       <c r="K9" s="24">
@@ -4712,58 +4711,58 @@
       <c r="L9" s="24">
         <v>10</v>
       </c>
-      <c r="M9" s="34">
+      <c r="M9" s="31">
         <v>0.3</v>
       </c>
-      <c r="N9" s="34">
+      <c r="N9" s="31">
         <v>1.3</v>
       </c>
-      <c r="O9" s="34">
+      <c r="O9" s="31">
         <v>1</v>
       </c>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="30"/>
       <c r="R9" s="24"/>
-      <c r="S9" s="33"/>
-      <c r="T9" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="U9" s="33"/>
-      <c r="V9" s="33"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="33"/>
-      <c r="Y9" s="33"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="30"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A10" s="24">
+      <c r="A10" s="25">
         <f t="shared" ref="A10" si="3">(B10*1000000) + (C10*100000) + D10</f>
         <v>10102003</v>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="32">
         <v>10</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="25">
         <v>1</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>2003</v>
       </c>
       <c r="E10" s="24">
         <v>2</v>
       </c>
-      <c r="F10" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="G10" s="34">
+      <c r="F10" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="G10" s="31">
         <v>100</v>
       </c>
       <c r="H10" s="24">
         <v>9</v>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="31">
         <v>40</v>
       </c>
-      <c r="J10" s="34">
+      <c r="J10" s="31">
         <v>10</v>
       </c>
       <c r="K10" s="24">
@@ -4772,58 +4771,58 @@
       <c r="L10" s="24">
         <v>10</v>
       </c>
-      <c r="M10" s="34">
+      <c r="M10" s="31">
         <v>0.3</v>
       </c>
-      <c r="N10" s="34">
+      <c r="N10" s="31">
         <v>1.3</v>
       </c>
-      <c r="O10" s="34">
+      <c r="O10" s="31">
         <v>1</v>
       </c>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="30"/>
       <c r="R10" s="24"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="U10" s="33"/>
-      <c r="V10" s="33"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="33"/>
-      <c r="Y10" s="33"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="U10" s="30"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="30"/>
+      <c r="X10" s="30"/>
+      <c r="Y10" s="30"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A11" s="24">
+      <c r="A11" s="25">
         <f t="shared" ref="A11" si="4">(B11*1000000) + (C11*10000) + D11</f>
         <v>10012004</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="32">
         <v>10</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="25">
         <v>1</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="25">
         <v>2004</v>
       </c>
       <c r="E11" s="24">
         <v>2</v>
       </c>
-      <c r="F11" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="G11" s="34">
+      <c r="F11" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="G11" s="31">
         <v>100</v>
       </c>
       <c r="H11" s="24">
         <v>9</v>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="31">
         <v>40</v>
       </c>
-      <c r="J11" s="34">
+      <c r="J11" s="31">
         <v>10</v>
       </c>
       <c r="K11" s="24">
@@ -4832,162 +4831,162 @@
       <c r="L11" s="24">
         <v>10</v>
       </c>
-      <c r="M11" s="34">
+      <c r="M11" s="31">
         <v>0.3</v>
       </c>
-      <c r="N11" s="34">
+      <c r="N11" s="31">
         <v>1.3</v>
       </c>
-      <c r="O11" s="34">
+      <c r="O11" s="31">
         <v>1</v>
       </c>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="30"/>
       <c r="R11" s="24"/>
-      <c r="S11" s="33"/>
-      <c r="T11" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="U11" s="33"/>
-      <c r="V11" s="33"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="33"/>
-      <c r="Y11" s="33"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="U11" s="30"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="30"/>
+      <c r="X11" s="30"/>
+      <c r="Y11" s="30"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A12" s="24"/>
-      <c r="B12" s="35"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="24"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
       <c r="E12" s="24"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="34"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="31"/>
       <c r="H12" s="24"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
       <c r="K12" s="24"/>
       <c r="L12" s="24"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="30"/>
       <c r="R12" s="24"/>
-      <c r="S12" s="33"/>
-      <c r="T12" s="33"/>
-      <c r="U12" s="33"/>
-      <c r="V12" s="33"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="33"/>
-      <c r="Y12" s="33"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="30"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="30"/>
+      <c r="X12" s="30"/>
+      <c r="Y12" s="30"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A13" s="24"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="34"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="24"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
       <c r="K13" s="24"/>
       <c r="L13" s="24"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="30"/>
       <c r="R13" s="24"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="33"/>
-      <c r="V13" s="33"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="33"/>
-      <c r="Y13" s="33"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="30"/>
+      <c r="X13" s="30"/>
+      <c r="Y13" s="30"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A14" s="24"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="34"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="31"/>
       <c r="H14" s="24"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
       <c r="K14" s="24"/>
       <c r="L14" s="24"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="30"/>
       <c r="R14" s="24"/>
-      <c r="S14" s="33"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="33"/>
-      <c r="V14" s="33"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="33"/>
-      <c r="Y14" s="33"/>
+      <c r="S14" s="30"/>
+      <c r="T14" s="30"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="30"/>
+      <c r="X14" s="30"/>
+      <c r="Y14" s="30"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A15" s="24"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="34"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="31"/>
       <c r="H15" s="24"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
       <c r="K15" s="24"/>
       <c r="L15" s="24"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="30"/>
+      <c r="Q15" s="30"/>
       <c r="R15" s="24"/>
-      <c r="S15" s="33"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="33"/>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
+      <c r="S15" s="30"/>
+      <c r="T15" s="30"/>
+      <c r="U15" s="30"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="30"/>
+      <c r="X15" s="30"/>
+      <c r="Y15" s="30"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="34"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="31"/>
       <c r="H16" s="24"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
       <c r="K16" s="24"/>
       <c r="L16" s="24"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="30"/>
       <c r="R16" s="24"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="33"/>
-      <c r="V16" s="33"/>
-      <c r="W16" s="33"/>
-      <c r="X16" s="33"/>
-      <c r="Y16" s="33"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="30"/>
+      <c r="X16" s="30"/>
+      <c r="Y16" s="30"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Data/DataTable/01_Character_Table_fix.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table_fix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F28103-719E-4983-9038-5F29ED932785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4A66FF-8136-49CD-B613-B367199F0C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -775,7 +775,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="135">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1249,10 +1249,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SIDE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1270,6 +1266,18 @@
   </si>
   <si>
     <t>Default_Defense</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Side</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default_Attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max_SP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1279,7 +1287,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="178" formatCode="0.0_);[Red]\(0.0\)"/>
+    <numFmt numFmtId="177" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1529,7 +1537,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -4372,28 +4380,28 @@
         <v>63</v>
       </c>
       <c r="E4" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="K4" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>130</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="K4" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>131</v>
       </c>
       <c r="M4" s="26" t="s">
         <v>99</v>

--- a/Assets/Data/DataTable/01_Character_Table_fix.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4A66FF-8136-49CD-B613-B367199F0C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D3C604-3C8F-4A3D-9DBA-39E4C0022A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1170,9 +1170,6 @@
     <t>Element_Charge_Rate</t>
   </si>
   <si>
-    <t>Element_Charge_Resiste</t>
-  </si>
-  <si>
     <t>Overload_Rate</t>
   </si>
   <si>
@@ -1278,6 +1275,10 @@
   </si>
   <si>
     <t>Max_SP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Charge_Resist</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3841,7 +3842,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" t="s">
         <v>72</v>
@@ -4219,7 +4220,7 @@
     <col min="15" max="15" width="21.125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="28" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18.5" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="21" bestFit="1" customWidth="1"/>
   </cols>
@@ -4246,7 +4247,7 @@
         <v>76</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>82</v>
@@ -4282,7 +4283,7 @@
         <v>93</v>
       </c>
       <c r="Q2" s="22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R2" s="22" t="s">
         <v>94</v>
@@ -4313,7 +4314,7 @@
         <v>70</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F3" s="29" t="s">
         <v>70</v>
@@ -4380,28 +4381,28 @@
         <v>63</v>
       </c>
       <c r="E4" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="I4" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="G4" s="26" t="s">
+      <c r="J4" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="K4" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="H4" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="K4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>129</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>130</v>
       </c>
       <c r="M4" s="26" t="s">
         <v>99</v>
@@ -4419,13 +4420,13 @@
         <v>103</v>
       </c>
       <c r="R4" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="S4" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="S4" s="26" t="s">
+      <c r="T4" s="26" t="s">
         <v>105</v>
-      </c>
-      <c r="T4" s="26" t="s">
-        <v>106</v>
       </c>
       <c r="U4" s="26"/>
       <c r="V4" s="26"/>
@@ -4451,7 +4452,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G5" s="31">
         <v>100</v>
@@ -4481,19 +4482,19 @@
         <v>1.3</v>
       </c>
       <c r="P5" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q5" s="30" t="s">
         <v>107</v>
-      </c>
-      <c r="Q5" s="30" t="s">
-        <v>108</v>
       </c>
       <c r="R5" s="31">
         <v>1</v>
       </c>
       <c r="S5" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="T5" s="25" t="s">
         <v>108</v>
-      </c>
-      <c r="T5" s="25" t="s">
-        <v>109</v>
       </c>
       <c r="U5" s="25"/>
       <c r="V5" s="25"/>
@@ -4519,7 +4520,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G6" s="31">
         <v>100</v>
@@ -4553,7 +4554,7 @@
       <c r="R6" s="24"/>
       <c r="S6" s="30"/>
       <c r="T6" s="25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U6" s="25"/>
       <c r="V6" s="25"/>
@@ -4579,7 +4580,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G7" s="31">
         <v>100</v>
@@ -4613,7 +4614,7 @@
       <c r="R7" s="24"/>
       <c r="S7" s="30"/>
       <c r="T7" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U7" s="30"/>
       <c r="V7" s="30"/>
@@ -4639,7 +4640,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G8" s="31">
         <v>100</v>
@@ -4673,7 +4674,7 @@
       <c r="R8" s="24"/>
       <c r="S8" s="30"/>
       <c r="T8" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="U8" s="30"/>
       <c r="V8" s="30"/>
@@ -4699,7 +4700,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G9" s="31">
         <v>100</v>
@@ -4733,7 +4734,7 @@
       <c r="R9" s="24"/>
       <c r="S9" s="30"/>
       <c r="T9" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="U9" s="30"/>
       <c r="V9" s="30"/>
@@ -4759,7 +4760,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G10" s="31">
         <v>100</v>
@@ -4793,7 +4794,7 @@
       <c r="R10" s="24"/>
       <c r="S10" s="30"/>
       <c r="T10" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U10" s="30"/>
       <c r="V10" s="30"/>
@@ -4819,7 +4820,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G11" s="31">
         <v>100</v>
@@ -4853,7 +4854,7 @@
       <c r="R11" s="24"/>
       <c r="S11" s="30"/>
       <c r="T11" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="U11" s="30"/>
       <c r="V11" s="30"/>

--- a/Assets/Data/DataTable/01_Character_Table_fix.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table_fix.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D3C604-3C8F-4A3D-9DBA-39E4C0022A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477453D7-F43E-4C76-A711-C6CC07E2FFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
     <sheet name="!Desc" sheetId="1" r:id="rId2"/>
-    <sheet name="!Sample" sheetId="3" r:id="rId3"/>
+    <sheet name="CharacterTable" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1137,10 +1137,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>속성 게이지 저항 계수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>속성 과부하 계수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1279,6 +1275,10 @@
   </si>
   <si>
     <t>Element_Charge_Resist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3842,7 +3842,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" t="s">
         <v>72</v>
@@ -4247,7 +4247,7 @@
         <v>76</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>82</v>
@@ -4283,16 +4283,16 @@
         <v>93</v>
       </c>
       <c r="Q2" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R2" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="S2" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="S2" s="22" t="s">
+      <c r="T2" s="22" t="s">
         <v>95</v>
-      </c>
-      <c r="T2" s="22" t="s">
-        <v>96</v>
       </c>
       <c r="U2" s="22"/>
       <c r="V2" s="22"/>
@@ -4314,7 +4314,7 @@
         <v>70</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F3" s="29" t="s">
         <v>70</v>
@@ -4347,16 +4347,16 @@
         <v>84</v>
       </c>
       <c r="P3" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q3" s="29" t="s">
         <v>97</v>
-      </c>
-      <c r="Q3" s="29" t="s">
-        <v>98</v>
       </c>
       <c r="R3" s="29" t="s">
         <v>84</v>
       </c>
       <c r="S3" s="29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T3" s="29" t="s">
         <v>70</v>
@@ -4381,52 +4381,52 @@
         <v>63</v>
       </c>
       <c r="E4" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="I4" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="G4" s="26" t="s">
+      <c r="J4" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="K4" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="L4" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="N4" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="O4" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="P4" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q4" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="R4" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="I4" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="K4" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="M4" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="N4" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="O4" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="P4" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q4" s="26" t="s">
+      <c r="S4" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="R4" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="S4" s="26" t="s">
+      <c r="T4" s="26" t="s">
         <v>104</v>
-      </c>
-      <c r="T4" s="26" t="s">
-        <v>105</v>
       </c>
       <c r="U4" s="26"/>
       <c r="V4" s="26"/>
@@ -4452,7 +4452,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G5" s="31">
         <v>100</v>
@@ -4482,19 +4482,19 @@
         <v>1.3</v>
       </c>
       <c r="P5" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q5" s="30" t="s">
         <v>106</v>
-      </c>
-      <c r="Q5" s="30" t="s">
-        <v>107</v>
       </c>
       <c r="R5" s="31">
         <v>1</v>
       </c>
       <c r="S5" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="T5" s="25" t="s">
         <v>107</v>
-      </c>
-      <c r="T5" s="25" t="s">
-        <v>108</v>
       </c>
       <c r="U5" s="25"/>
       <c r="V5" s="25"/>
@@ -4520,7 +4520,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G6" s="31">
         <v>100</v>
@@ -4554,7 +4554,7 @@
       <c r="R6" s="24"/>
       <c r="S6" s="30"/>
       <c r="T6" s="25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U6" s="25"/>
       <c r="V6" s="25"/>
@@ -4580,7 +4580,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G7" s="31">
         <v>100</v>
@@ -4614,7 +4614,7 @@
       <c r="R7" s="24"/>
       <c r="S7" s="30"/>
       <c r="T7" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U7" s="30"/>
       <c r="V7" s="30"/>
@@ -4640,7 +4640,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G8" s="31">
         <v>100</v>
@@ -4674,7 +4674,7 @@
       <c r="R8" s="24"/>
       <c r="S8" s="30"/>
       <c r="T8" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U8" s="30"/>
       <c r="V8" s="30"/>
@@ -4700,7 +4700,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G9" s="31">
         <v>100</v>
@@ -4734,7 +4734,7 @@
       <c r="R9" s="24"/>
       <c r="S9" s="30"/>
       <c r="T9" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="U9" s="30"/>
       <c r="V9" s="30"/>
@@ -4760,7 +4760,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G10" s="31">
         <v>100</v>
@@ -4794,7 +4794,7 @@
       <c r="R10" s="24"/>
       <c r="S10" s="30"/>
       <c r="T10" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="U10" s="30"/>
       <c r="V10" s="30"/>
@@ -4820,7 +4820,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G11" s="31">
         <v>100</v>
@@ -4854,7 +4854,7 @@
       <c r="R11" s="24"/>
       <c r="S11" s="30"/>
       <c r="T11" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U11" s="30"/>
       <c r="V11" s="30"/>

--- a/Assets/Data/DataTable/01_Character_Table_fix.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table_fix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477453D7-F43E-4C76-A711-C6CC07E2FFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB656FF-DCF1-49AD-8FE8-CF3B5154DC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -1278,7 +1278,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>]</t>
+    <t>속성 게이지 저항 계수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/Assets/Data/DataTable/01_Character_Table_fix.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB656FF-DCF1-49AD-8FE8-CF3B5154DC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E629431-8689-4C45-A8CF-8E20DE72A941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -775,7 +775,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="136">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1172,9 +1172,6 @@
     <t>Asset_File</t>
   </si>
   <si>
-    <t>20010001,20010002,20010003</t>
-  </si>
-  <si>
     <t>1.0,1.0,1.0,1.0,1.0,1.0</t>
   </si>
   <si>
@@ -1199,34 +1196,6 @@
     <t>penguin_Berserker</t>
   </si>
   <si>
-    <t>Character_Name_1001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character_Name_1002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character_Name_1003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monster_Name_2001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monster_Name_2002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monster_Name_2003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monster_Name_2004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>속성 게이지 효율 계수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1279,6 +1248,43 @@
   </si>
   <si>
     <t>속성 게이지 저항 계수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHARACTER_NAME_1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHARACTER_NAME_1002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHARACTER_NAME_1003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MONSTER_NAME_2001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MONSTER_NAME_2002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MONSTER_NAME_2003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MONSTER_NAME_2004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20012001,20012002,
+20012003,20012004</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3842,7 +3848,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C13" t="s">
         <v>72</v>
@@ -4208,7 +4214,7 @@
     <col min="3" max="3" width="4.875" style="33" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.125" style="33" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.625" bestFit="1" customWidth="1"/>
@@ -4218,7 +4224,7 @@
     <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="21.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="28" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="28" style="33" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="20.125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18.5" bestFit="1" customWidth="1"/>
@@ -4232,6 +4238,7 @@
       <c r="B1"/>
       <c r="C1"/>
       <c r="D1"/>
+      <c r="P1"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
@@ -4247,7 +4254,7 @@
         <v>76</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>82</v>
@@ -4283,10 +4290,10 @@
         <v>93</v>
       </c>
       <c r="Q2" s="22" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="R2" s="22" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="S2" s="22" t="s">
         <v>94</v>
@@ -4314,7 +4321,7 @@
         <v>70</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F3" s="29" t="s">
         <v>70</v>
@@ -4381,28 +4388,28 @@
         <v>63</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="K4" s="26" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="L4" s="26" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="M4" s="26" t="s">
         <v>98</v>
@@ -4420,7 +4427,7 @@
         <v>102</v>
       </c>
       <c r="R4" s="26" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="S4" s="26" t="s">
         <v>103</v>
@@ -4434,7 +4441,7 @@
       <c r="X4" s="26"/>
       <c r="Y4" s="26"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" ht="33" x14ac:dyDescent="0.3">
       <c r="A5" s="25">
         <f>(B5*1000000) + (C5*10000) + D5</f>
         <v>10001001</v>
@@ -4451,8 +4458,8 @@
       <c r="E5" s="24">
         <v>1</v>
       </c>
-      <c r="F5" s="30" t="s">
-        <v>114</v>
+      <c r="F5" s="24" t="s">
+        <v>127</v>
       </c>
       <c r="G5" s="31">
         <v>100</v>
@@ -4481,20 +4488,20 @@
       <c r="O5" s="31">
         <v>1.3</v>
       </c>
-      <c r="P5" s="30" t="s">
+      <c r="P5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q5" s="30" t="s">
         <v>105</v>
-      </c>
-      <c r="Q5" s="30" t="s">
-        <v>106</v>
       </c>
       <c r="R5" s="31">
         <v>1</v>
       </c>
       <c r="S5" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="T5" s="25" t="s">
         <v>106</v>
-      </c>
-      <c r="T5" s="25" t="s">
-        <v>107</v>
       </c>
       <c r="U5" s="25"/>
       <c r="V5" s="25"/>
@@ -4519,8 +4526,8 @@
       <c r="E6" s="24">
         <v>1</v>
       </c>
-      <c r="F6" s="30" t="s">
-        <v>115</v>
+      <c r="F6" s="24" t="s">
+        <v>128</v>
       </c>
       <c r="G6" s="31">
         <v>100</v>
@@ -4549,12 +4556,12 @@
       <c r="O6" s="31">
         <v>1.3</v>
       </c>
-      <c r="P6" s="30"/>
+      <c r="P6" s="25"/>
       <c r="Q6" s="30"/>
       <c r="R6" s="24"/>
       <c r="S6" s="30"/>
       <c r="T6" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U6" s="25"/>
       <c r="V6" s="25"/>
@@ -4579,8 +4586,8 @@
       <c r="E7" s="24">
         <v>1</v>
       </c>
-      <c r="F7" s="30" t="s">
-        <v>116</v>
+      <c r="F7" s="24" t="s">
+        <v>129</v>
       </c>
       <c r="G7" s="31">
         <v>100</v>
@@ -4609,12 +4616,12 @@
       <c r="O7" s="31">
         <v>1.3</v>
       </c>
-      <c r="P7" s="30"/>
+      <c r="P7" s="25"/>
       <c r="Q7" s="30"/>
       <c r="R7" s="24"/>
       <c r="S7" s="30"/>
       <c r="T7" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U7" s="30"/>
       <c r="V7" s="30"/>
@@ -4639,8 +4646,8 @@
       <c r="E8" s="24">
         <v>2</v>
       </c>
-      <c r="F8" s="30" t="s">
-        <v>117</v>
+      <c r="F8" s="24" t="s">
+        <v>130</v>
       </c>
       <c r="G8" s="31">
         <v>100</v>
@@ -4669,12 +4676,12 @@
       <c r="O8" s="31">
         <v>1</v>
       </c>
-      <c r="P8" s="30"/>
+      <c r="P8" s="25"/>
       <c r="Q8" s="30"/>
       <c r="R8" s="24"/>
       <c r="S8" s="30"/>
       <c r="T8" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U8" s="30"/>
       <c r="V8" s="30"/>
@@ -4699,8 +4706,8 @@
       <c r="E9" s="24">
         <v>2</v>
       </c>
-      <c r="F9" s="30" t="s">
-        <v>118</v>
+      <c r="F9" s="24" t="s">
+        <v>131</v>
       </c>
       <c r="G9" s="31">
         <v>100</v>
@@ -4729,12 +4736,12 @@
       <c r="O9" s="31">
         <v>1</v>
       </c>
-      <c r="P9" s="30"/>
+      <c r="P9" s="25"/>
       <c r="Q9" s="30"/>
       <c r="R9" s="24"/>
       <c r="S9" s="30"/>
       <c r="T9" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U9" s="30"/>
       <c r="V9" s="30"/>
@@ -4759,8 +4766,8 @@
       <c r="E10" s="24">
         <v>2</v>
       </c>
-      <c r="F10" s="30" t="s">
-        <v>119</v>
+      <c r="F10" s="24" t="s">
+        <v>132</v>
       </c>
       <c r="G10" s="31">
         <v>100</v>
@@ -4789,12 +4796,12 @@
       <c r="O10" s="31">
         <v>1</v>
       </c>
-      <c r="P10" s="30"/>
+      <c r="P10" s="25"/>
       <c r="Q10" s="30"/>
       <c r="R10" s="24"/>
       <c r="S10" s="30"/>
       <c r="T10" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="U10" s="30"/>
       <c r="V10" s="30"/>
@@ -4819,8 +4826,8 @@
       <c r="E11" s="24">
         <v>2</v>
       </c>
-      <c r="F11" s="30" t="s">
-        <v>120</v>
+      <c r="F11" s="24" t="s">
+        <v>133</v>
       </c>
       <c r="G11" s="31">
         <v>100</v>
@@ -4849,12 +4856,12 @@
       <c r="O11" s="31">
         <v>1</v>
       </c>
-      <c r="P11" s="30"/>
+      <c r="P11" s="25"/>
       <c r="Q11" s="30"/>
       <c r="R11" s="24"/>
       <c r="S11" s="30"/>
       <c r="T11" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="U11" s="30"/>
       <c r="V11" s="30"/>
@@ -4878,7 +4885,7 @@
       <c r="M12" s="31"/>
       <c r="N12" s="31"/>
       <c r="O12" s="31"/>
-      <c r="P12" s="30"/>
+      <c r="P12" s="25"/>
       <c r="Q12" s="30"/>
       <c r="R12" s="24"/>
       <c r="S12" s="30"/>
@@ -4895,7 +4902,9 @@
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
       <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
+      <c r="F13" s="30" t="s">
+        <v>134</v>
+      </c>
       <c r="G13" s="31"/>
       <c r="H13" s="24"/>
       <c r="I13" s="31"/>
@@ -4905,7 +4914,7 @@
       <c r="M13" s="31"/>
       <c r="N13" s="31"/>
       <c r="O13" s="31"/>
-      <c r="P13" s="30"/>
+      <c r="P13" s="25"/>
       <c r="Q13" s="30"/>
       <c r="R13" s="24"/>
       <c r="S13" s="30"/>
@@ -4932,7 +4941,7 @@
       <c r="M14" s="31"/>
       <c r="N14" s="31"/>
       <c r="O14" s="31"/>
-      <c r="P14" s="30"/>
+      <c r="P14" s="25"/>
       <c r="Q14" s="30"/>
       <c r="R14" s="24"/>
       <c r="S14" s="30"/>
@@ -4959,7 +4968,7 @@
       <c r="M15" s="31"/>
       <c r="N15" s="31"/>
       <c r="O15" s="31"/>
-      <c r="P15" s="30"/>
+      <c r="P15" s="25"/>
       <c r="Q15" s="30"/>
       <c r="R15" s="24"/>
       <c r="S15" s="30"/>
@@ -4986,7 +4995,7 @@
       <c r="M16" s="31"/>
       <c r="N16" s="31"/>
       <c r="O16" s="31"/>
-      <c r="P16" s="30"/>
+      <c r="P16" s="25"/>
       <c r="Q16" s="30"/>
       <c r="R16" s="24"/>
       <c r="S16" s="30"/>

--- a/Assets/Data/DataTable/01_Character_Table_fix.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E629431-8689-4C45-A8CF-8E20DE72A941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B4ABDF-310E-4380-BE35-CEEE20E509FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1292,9 +1292,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0.0_);[Red]\(0.0\)"/>
+    <numFmt numFmtId="178" formatCode="00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1450,7 +1451,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1551,6 +1552,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4211,8 +4218,8 @@
   <cols>
     <col min="1" max="1" width="15.5" style="33" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.375" style="33" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.875" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.125" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" style="35" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" style="33" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.375" bestFit="1" customWidth="1"/>
@@ -4449,7 +4456,7 @@
       <c r="B5" s="32">
         <v>10</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="34">
         <v>0</v>
       </c>
       <c r="D5" s="25">
@@ -4517,7 +4524,7 @@
       <c r="B6" s="32">
         <v>10</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="34">
         <v>0</v>
       </c>
       <c r="D6" s="25">
@@ -4577,7 +4584,7 @@
       <c r="B7" s="33">
         <v>10</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="34">
         <v>0</v>
       </c>
       <c r="D7" s="25">
@@ -4637,7 +4644,7 @@
       <c r="B8" s="32">
         <v>10</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="34">
         <v>1</v>
       </c>
       <c r="D8" s="25">
@@ -4697,7 +4704,7 @@
       <c r="B9" s="32">
         <v>10</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="34">
         <v>1</v>
       </c>
       <c r="D9" s="25">
@@ -4757,7 +4764,7 @@
       <c r="B10" s="32">
         <v>10</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="34">
         <v>1</v>
       </c>
       <c r="D10" s="25">
@@ -4817,7 +4824,7 @@
       <c r="B11" s="32">
         <v>10</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="34">
         <v>1</v>
       </c>
       <c r="D11" s="25">
@@ -4872,7 +4879,7 @@
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="25"/>
       <c r="B12" s="32"/>
-      <c r="C12" s="25"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="25"/>
       <c r="E12" s="24"/>
       <c r="F12" s="30"/>
@@ -4899,7 +4906,7 @@
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="25"/>
       <c r="B13" s="32"/>
-      <c r="C13" s="25"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="25"/>
       <c r="E13" s="30"/>
       <c r="F13" s="30" t="s">
@@ -4928,7 +4935,7 @@
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="25"/>
       <c r="B14" s="32"/>
-      <c r="C14" s="25"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="25"/>
       <c r="E14" s="30"/>
       <c r="F14" s="30"/>
@@ -4955,7 +4962,7 @@
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="25"/>
       <c r="B15" s="32"/>
-      <c r="C15" s="25"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="25"/>
       <c r="E15" s="30"/>
       <c r="F15" s="30"/>
@@ -4982,7 +4989,7 @@
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="25"/>
       <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="25"/>
       <c r="E16" s="30"/>
       <c r="F16" s="30"/>

--- a/Assets/Data/DataTable/01_Character_Table_fix.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table_fix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B4ABDF-310E-4380-BE35-CEEE20E509FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADC4E29-72A9-4CA6-84AD-AD4A97C73F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -1283,7 +1283,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20012001,20012002,
+    <t>20001001,
+20012001,20012002,
 20012003,20012004</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4448,7 +4449,7 @@
       <c r="X4" s="26"/>
       <c r="Y4" s="26"/>
     </row>
-    <row r="5" spans="1:25" ht="33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A5" s="25">
         <f>(B5*1000000) + (C5*10000) + D5</f>
         <v>10001001</v>

--- a/Assets/Data/DataTable/01_Character_Table_fix.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table_fix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADC4E29-72A9-4CA6-84AD-AD4A97C73F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332F709D-462D-49F6-846C-2B40EA1088D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -1184,9 +1184,6 @@
     <t>player_Commissar</t>
   </si>
   <si>
-    <t>penguin_Rfleman</t>
-  </si>
-  <si>
     <t>penguin_Sniper</t>
   </si>
   <si>
@@ -1286,6 +1283,10 @@
     <t>20001001,
 20012001,20012002,
 20012003,20012004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>penguin_Rifleman</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3856,7 +3857,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C13" t="s">
         <v>72</v>
@@ -4262,7 +4263,7 @@
         <v>76</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>82</v>
@@ -4298,10 +4299,10 @@
         <v>93</v>
       </c>
       <c r="Q2" s="22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R2" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="S2" s="22" t="s">
         <v>94</v>
@@ -4329,7 +4330,7 @@
         <v>70</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F3" s="29" t="s">
         <v>70</v>
@@ -4396,28 +4397,28 @@
         <v>63</v>
       </c>
       <c r="E4" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="I4" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="G4" s="26" t="s">
+      <c r="J4" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="K4" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="H4" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="K4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>119</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>120</v>
       </c>
       <c r="M4" s="26" t="s">
         <v>98</v>
@@ -4435,7 +4436,7 @@
         <v>102</v>
       </c>
       <c r="R4" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="S4" s="26" t="s">
         <v>103</v>
@@ -4467,7 +4468,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G5" s="31">
         <v>100</v>
@@ -4497,7 +4498,7 @@
         <v>1.3</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q5" s="30" t="s">
         <v>105</v>
@@ -4535,7 +4536,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G6" s="31">
         <v>100</v>
@@ -4595,7 +4596,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G7" s="31">
         <v>100</v>
@@ -4655,7 +4656,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G8" s="31">
         <v>100</v>
@@ -4689,7 +4690,7 @@
       <c r="R8" s="24"/>
       <c r="S8" s="30"/>
       <c r="T8" s="30" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="U8" s="30"/>
       <c r="V8" s="30"/>
@@ -4715,7 +4716,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G9" s="31">
         <v>100</v>
@@ -4749,7 +4750,7 @@
       <c r="R9" s="24"/>
       <c r="S9" s="30"/>
       <c r="T9" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U9" s="30"/>
       <c r="V9" s="30"/>
@@ -4775,7 +4776,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G10" s="31">
         <v>100</v>
@@ -4809,7 +4810,7 @@
       <c r="R10" s="24"/>
       <c r="S10" s="30"/>
       <c r="T10" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U10" s="30"/>
       <c r="V10" s="30"/>
@@ -4835,7 +4836,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G11" s="31">
         <v>100</v>
@@ -4869,7 +4870,7 @@
       <c r="R11" s="24"/>
       <c r="S11" s="30"/>
       <c r="T11" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="U11" s="30"/>
       <c r="V11" s="30"/>
@@ -4911,7 +4912,7 @@
       <c r="D13" s="25"/>
       <c r="E13" s="30"/>
       <c r="F13" s="30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G13" s="31"/>
       <c r="H13" s="24"/>

--- a/Assets/Data/DataTable/01_Character_Table_fix.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332F709D-462D-49F6-846C-2B40EA1088D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF8A5A9-5AA5-4397-86E9-B6A1DECF71EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4520,7 +4520,7 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
-        <f>(B6*1000000) + (C6*100000) + D6</f>
+        <f t="shared" ref="A6:A11" si="0">(B6*1000000) + (C6*10000) + D6</f>
         <v>10001002</v>
       </c>
       <c r="B6" s="32">
@@ -4580,7 +4580,7 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
-        <f t="shared" ref="A7" si="0">(B7*1000000) + (C7*10000) + D7</f>
+        <f t="shared" si="0"/>
         <v>10001003</v>
       </c>
       <c r="B7" s="33">
@@ -4640,8 +4640,8 @@
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
-        <f t="shared" ref="A8" si="1">(B8*1000000) + (C8*100000) + D8</f>
-        <v>10102001</v>
+        <f t="shared" si="0"/>
+        <v>10012001</v>
       </c>
       <c r="B8" s="32">
         <v>10</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
-        <f t="shared" ref="A9" si="2">(B9*1000000) + (C9*10000) + D9</f>
+        <f t="shared" si="0"/>
         <v>10012002</v>
       </c>
       <c r="B9" s="32">
@@ -4760,8 +4760,8 @@
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
-        <f t="shared" ref="A10" si="3">(B10*1000000) + (C10*100000) + D10</f>
-        <v>10102003</v>
+        <f t="shared" si="0"/>
+        <v>10012003</v>
       </c>
       <c r="B10" s="32">
         <v>10</v>
@@ -4820,7 +4820,7 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
-        <f t="shared" ref="A11" si="4">(B11*1000000) + (C11*10000) + D11</f>
+        <f t="shared" si="0"/>
         <v>10012004</v>
       </c>
       <c r="B11" s="32">
@@ -5018,7 +5018,8 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">

--- a/Assets/Data/DataTable/01_Character_Table_fix.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table_fix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF8A5A9-5AA5-4397-86E9-B6A1DECF71EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74FB565-1153-4C7A-916D-17CF771E052F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -775,7 +775,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="142">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1287,6 +1287,30 @@
   </si>
   <si>
     <t>penguin_Rifleman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>피해 배율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는 피해 배율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP 소모량 증가 배율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage_Multiplier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage_Taken_Multiplier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP_Consumption_Rate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1453,7 +1477,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1560,6 +1584,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4215,7 +4245,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:AB16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5" style="33" bestFit="1" customWidth="1"/>
@@ -4237,10 +4267,13 @@
     <col min="17" max="17" width="18.5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="20.125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.125" style="37" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23" style="37" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.5" style="37" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>81</v>
       </c>
@@ -4248,8 +4281,11 @@
       <c r="C1"/>
       <c r="D1"/>
       <c r="P1"/>
+      <c r="T1"/>
+      <c r="U1"/>
+      <c r="V1"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>77</v>
       </c>
@@ -4308,15 +4344,24 @@
         <v>94</v>
       </c>
       <c r="T2" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="U2" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="V2" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="W2" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
       <c r="X2" s="22"/>
       <c r="Y2" s="22"/>
+      <c r="Z2" s="22"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="22"/>
     </row>
-    <row r="3" spans="1:25" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
         <v>70</v>
       </c>
@@ -4375,15 +4420,24 @@
         <v>97</v>
       </c>
       <c r="T3" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="U3" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="V3" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="W3" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="29"/>
       <c r="X3" s="29"/>
       <c r="Y3" s="29"/>
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="29"/>
+      <c r="AB3" s="29"/>
     </row>
-    <row r="4" spans="1:25" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>55</v>
       </c>
@@ -4442,15 +4496,24 @@
         <v>103</v>
       </c>
       <c r="T4" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="U4" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="V4" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="W4" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="U4" s="26"/>
-      <c r="V4" s="26"/>
-      <c r="W4" s="26"/>
       <c r="X4" s="26"/>
       <c r="Y4" s="26"/>
+      <c r="Z4" s="26"/>
+      <c r="AA4" s="26"/>
+      <c r="AB4" s="26"/>
     </row>
-    <row r="5" spans="1:25" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A5" s="25">
         <f>(B5*1000000) + (C5*10000) + D5</f>
         <v>10001001</v>
@@ -4509,16 +4572,25 @@
       <c r="S5" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="T5" s="25" t="s">
+      <c r="T5" s="36">
+        <v>1</v>
+      </c>
+      <c r="U5" s="36">
+        <v>1</v>
+      </c>
+      <c r="V5" s="36">
+        <v>1</v>
+      </c>
+      <c r="W5" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="U5" s="25"/>
-      <c r="V5" s="25"/>
-      <c r="W5" s="25"/>
       <c r="X5" s="25"/>
       <c r="Y5" s="25"/>
+      <c r="Z5" s="25"/>
+      <c r="AA5" s="25"/>
+      <c r="AB5" s="25"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <f t="shared" ref="A6:A11" si="0">(B6*1000000) + (C6*10000) + D6</f>
         <v>10001002</v>
@@ -4569,16 +4641,19 @@
       <c r="Q6" s="30"/>
       <c r="R6" s="24"/>
       <c r="S6" s="30"/>
-      <c r="T6" s="25" t="s">
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="U6" s="25"/>
-      <c r="V6" s="25"/>
-      <c r="W6" s="25"/>
       <c r="X6" s="25"/>
       <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
         <f t="shared" si="0"/>
         <v>10001003</v>
@@ -4629,16 +4704,19 @@
       <c r="Q7" s="30"/>
       <c r="R7" s="24"/>
       <c r="S7" s="30"/>
-      <c r="T7" s="30" t="s">
+      <c r="T7" s="36"/>
+      <c r="U7" s="36"/>
+      <c r="V7" s="36"/>
+      <c r="W7" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
       <c r="X7" s="30"/>
       <c r="Y7" s="30"/>
+      <c r="Z7" s="30"/>
+      <c r="AA7" s="30"/>
+      <c r="AB7" s="30"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
         <f t="shared" si="0"/>
         <v>10012001</v>
@@ -4689,16 +4767,19 @@
       <c r="Q8" s="30"/>
       <c r="R8" s="24"/>
       <c r="S8" s="30"/>
-      <c r="T8" s="30" t="s">
+      <c r="T8" s="36"/>
+      <c r="U8" s="36"/>
+      <c r="V8" s="36"/>
+      <c r="W8" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="U8" s="30"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="30"/>
       <c r="X8" s="30"/>
       <c r="Y8" s="30"/>
+      <c r="Z8" s="30"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="30"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
         <f t="shared" si="0"/>
         <v>10012002</v>
@@ -4749,16 +4830,19 @@
       <c r="Q9" s="30"/>
       <c r="R9" s="24"/>
       <c r="S9" s="30"/>
-      <c r="T9" s="30" t="s">
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="36"/>
+      <c r="W9" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="U9" s="30"/>
-      <c r="V9" s="30"/>
-      <c r="W9" s="30"/>
       <c r="X9" s="30"/>
       <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="30"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <f t="shared" si="0"/>
         <v>10012003</v>
@@ -4809,16 +4893,19 @@
       <c r="Q10" s="30"/>
       <c r="R10" s="24"/>
       <c r="S10" s="30"/>
-      <c r="T10" s="30" t="s">
+      <c r="T10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="36"/>
+      <c r="W10" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="U10" s="30"/>
-      <c r="V10" s="30"/>
-      <c r="W10" s="30"/>
       <c r="X10" s="30"/>
       <c r="Y10" s="30"/>
+      <c r="Z10" s="30"/>
+      <c r="AA10" s="30"/>
+      <c r="AB10" s="30"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
         <f t="shared" si="0"/>
         <v>10012004</v>
@@ -4869,16 +4956,19 @@
       <c r="Q11" s="30"/>
       <c r="R11" s="24"/>
       <c r="S11" s="30"/>
-      <c r="T11" s="30" t="s">
+      <c r="T11" s="36"/>
+      <c r="U11" s="36"/>
+      <c r="V11" s="36"/>
+      <c r="W11" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="U11" s="30"/>
-      <c r="V11" s="30"/>
-      <c r="W11" s="30"/>
       <c r="X11" s="30"/>
       <c r="Y11" s="30"/>
+      <c r="Z11" s="30"/>
+      <c r="AA11" s="30"/>
+      <c r="AB11" s="30"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" s="25"/>
       <c r="B12" s="32"/>
       <c r="C12" s="34"/>
@@ -4898,14 +4988,17 @@
       <c r="Q12" s="30"/>
       <c r="R12" s="24"/>
       <c r="S12" s="30"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="36"/>
       <c r="W12" s="30"/>
       <c r="X12" s="30"/>
       <c r="Y12" s="30"/>
+      <c r="Z12" s="30"/>
+      <c r="AA12" s="30"/>
+      <c r="AB12" s="30"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" s="25"/>
       <c r="B13" s="32"/>
       <c r="C13" s="34"/>
@@ -4927,14 +5020,17 @@
       <c r="Q13" s="30"/>
       <c r="R13" s="24"/>
       <c r="S13" s="30"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="30"/>
-      <c r="V13" s="30"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="36"/>
+      <c r="V13" s="36"/>
       <c r="W13" s="30"/>
       <c r="X13" s="30"/>
       <c r="Y13" s="30"/>
+      <c r="Z13" s="30"/>
+      <c r="AA13" s="30"/>
+      <c r="AB13" s="30"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" s="25"/>
       <c r="B14" s="32"/>
       <c r="C14" s="34"/>
@@ -4954,14 +5050,17 @@
       <c r="Q14" s="30"/>
       <c r="R14" s="24"/>
       <c r="S14" s="30"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="30"/>
-      <c r="V14" s="30"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="36"/>
+      <c r="V14" s="36"/>
       <c r="W14" s="30"/>
       <c r="X14" s="30"/>
       <c r="Y14" s="30"/>
+      <c r="Z14" s="30"/>
+      <c r="AA14" s="30"/>
+      <c r="AB14" s="30"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" s="25"/>
       <c r="B15" s="32"/>
       <c r="C15" s="34"/>
@@ -4981,14 +5080,17 @@
       <c r="Q15" s="30"/>
       <c r="R15" s="24"/>
       <c r="S15" s="30"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="30"/>
-      <c r="V15" s="30"/>
+      <c r="T15" s="36"/>
+      <c r="U15" s="36"/>
+      <c r="V15" s="36"/>
       <c r="W15" s="30"/>
       <c r="X15" s="30"/>
       <c r="Y15" s="30"/>
+      <c r="Z15" s="30"/>
+      <c r="AA15" s="30"/>
+      <c r="AB15" s="30"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16" s="25"/>
       <c r="B16" s="25"/>
       <c r="C16" s="34"/>
@@ -5008,12 +5110,15 @@
       <c r="Q16" s="30"/>
       <c r="R16" s="24"/>
       <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="30"/>
-      <c r="V16" s="30"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="36"/>
+      <c r="V16" s="36"/>
       <c r="W16" s="30"/>
       <c r="X16" s="30"/>
       <c r="Y16" s="30"/>
+      <c r="Z16" s="30"/>
+      <c r="AA16" s="30"/>
+      <c r="AB16" s="30"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5022,12 +5127,12 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D44D287-4A0D-4E30-B02E-F978C229F037}">
           <x14:formula1>
             <xm:f>'!Logic'!$A$5:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>A3:L3</xm:sqref>
+          <xm:sqref>A3:XFD3</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Assets/Data/DataTable/01_Character_Table_fix.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74FB565-1153-4C7A-916D-17CF771E052F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F1BC96-E3C4-4EB6-97BB-C8C9ABED0A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -775,7 +775,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="136">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1287,30 +1287,6 @@
   </si>
   <si>
     <t>penguin_Rifleman</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>피해 배율</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>받는 피해 배율</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SP 소모량 증가 배율</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage_Multiplier</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage_Taken_Multiplier</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SP_Consumption_Rate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1477,7 +1453,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1584,12 +1560,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4245,7 +4215,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5" style="33" bestFit="1" customWidth="1"/>
@@ -4267,13 +4237,10 @@
     <col min="17" max="17" width="18.5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="20.125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.125" style="37" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="23" style="37" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.5" style="37" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>81</v>
       </c>
@@ -4281,11 +4248,8 @@
       <c r="C1"/>
       <c r="D1"/>
       <c r="P1"/>
-      <c r="T1"/>
-      <c r="U1"/>
-      <c r="V1"/>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>77</v>
       </c>
@@ -4344,24 +4308,15 @@
         <v>94</v>
       </c>
       <c r="T2" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="U2" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="V2" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="W2" s="22" t="s">
         <v>95</v>
       </c>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="22"/>
       <c r="X2" s="22"/>
       <c r="Y2" s="22"/>
-      <c r="Z2" s="22"/>
-      <c r="AA2" s="22"/>
-      <c r="AB2" s="22"/>
     </row>
-    <row r="3" spans="1:28" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
         <v>70</v>
       </c>
@@ -4420,24 +4375,15 @@
         <v>97</v>
       </c>
       <c r="T3" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="U3" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="V3" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="W3" s="29" t="s">
         <v>70</v>
       </c>
+      <c r="U3" s="29"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="29"/>
       <c r="X3" s="29"/>
       <c r="Y3" s="29"/>
-      <c r="Z3" s="29"/>
-      <c r="AA3" s="29"/>
-      <c r="AB3" s="29"/>
     </row>
-    <row r="4" spans="1:28" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>55</v>
       </c>
@@ -4496,24 +4442,15 @@
         <v>103</v>
       </c>
       <c r="T4" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="U4" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="V4" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="W4" s="26" t="s">
         <v>104</v>
       </c>
+      <c r="U4" s="26"/>
+      <c r="V4" s="26"/>
+      <c r="W4" s="26"/>
       <c r="X4" s="26"/>
       <c r="Y4" s="26"/>
-      <c r="Z4" s="26"/>
-      <c r="AA4" s="26"/>
-      <c r="AB4" s="26"/>
     </row>
-    <row r="5" spans="1:28" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A5" s="25">
         <f>(B5*1000000) + (C5*10000) + D5</f>
         <v>10001001</v>
@@ -4572,25 +4509,16 @@
       <c r="S5" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="T5" s="36">
-        <v>1</v>
-      </c>
-      <c r="U5" s="36">
-        <v>1</v>
-      </c>
-      <c r="V5" s="36">
-        <v>1</v>
-      </c>
-      <c r="W5" s="25" t="s">
+      <c r="T5" s="25" t="s">
         <v>106</v>
       </c>
+      <c r="U5" s="25"/>
+      <c r="V5" s="25"/>
+      <c r="W5" s="25"/>
       <c r="X5" s="25"/>
       <c r="Y5" s="25"/>
-      <c r="Z5" s="25"/>
-      <c r="AA5" s="25"/>
-      <c r="AB5" s="25"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <f t="shared" ref="A6:A11" si="0">(B6*1000000) + (C6*10000) + D6</f>
         <v>10001002</v>
@@ -4641,19 +4569,16 @@
       <c r="Q6" s="30"/>
       <c r="R6" s="24"/>
       <c r="S6" s="30"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="36"/>
-      <c r="V6" s="36"/>
-      <c r="W6" s="25" t="s">
+      <c r="T6" s="25" t="s">
         <v>107</v>
       </c>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="25"/>
       <c r="X6" s="25"/>
       <c r="Y6" s="25"/>
-      <c r="Z6" s="25"/>
-      <c r="AA6" s="25"/>
-      <c r="AB6" s="25"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
         <f t="shared" si="0"/>
         <v>10001003</v>
@@ -4704,19 +4629,16 @@
       <c r="Q7" s="30"/>
       <c r="R7" s="24"/>
       <c r="S7" s="30"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="36"/>
-      <c r="V7" s="36"/>
-      <c r="W7" s="30" t="s">
+      <c r="T7" s="30" t="s">
         <v>108</v>
       </c>
+      <c r="U7" s="30"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
       <c r="X7" s="30"/>
       <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="30"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
         <f t="shared" si="0"/>
         <v>10012001</v>
@@ -4767,19 +4689,16 @@
       <c r="Q8" s="30"/>
       <c r="R8" s="24"/>
       <c r="S8" s="30"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="36"/>
-      <c r="V8" s="36"/>
-      <c r="W8" s="30" t="s">
+      <c r="T8" s="30" t="s">
         <v>135</v>
       </c>
+      <c r="U8" s="30"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="30"/>
       <c r="X8" s="30"/>
       <c r="Y8" s="30"/>
-      <c r="Z8" s="30"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
         <f t="shared" si="0"/>
         <v>10012002</v>
@@ -4830,19 +4749,16 @@
       <c r="Q9" s="30"/>
       <c r="R9" s="24"/>
       <c r="S9" s="30"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="30" t="s">
+      <c r="T9" s="30" t="s">
         <v>109</v>
       </c>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
       <c r="X9" s="30"/>
       <c r="Y9" s="30"/>
-      <c r="Z9" s="30"/>
-      <c r="AA9" s="30"/>
-      <c r="AB9" s="30"/>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <f t="shared" si="0"/>
         <v>10012003</v>
@@ -4893,19 +4809,16 @@
       <c r="Q10" s="30"/>
       <c r="R10" s="24"/>
       <c r="S10" s="30"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="36"/>
-      <c r="V10" s="36"/>
-      <c r="W10" s="30" t="s">
+      <c r="T10" s="30" t="s">
         <v>110</v>
       </c>
+      <c r="U10" s="30"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="30"/>
       <c r="X10" s="30"/>
       <c r="Y10" s="30"/>
-      <c r="Z10" s="30"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
         <f t="shared" si="0"/>
         <v>10012004</v>
@@ -4956,19 +4869,16 @@
       <c r="Q11" s="30"/>
       <c r="R11" s="24"/>
       <c r="S11" s="30"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="36"/>
-      <c r="V11" s="36"/>
-      <c r="W11" s="30" t="s">
+      <c r="T11" s="30" t="s">
         <v>111</v>
       </c>
+      <c r="U11" s="30"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="30"/>
       <c r="X11" s="30"/>
       <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="30"/>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="25"/>
       <c r="B12" s="32"/>
       <c r="C12" s="34"/>
@@ -4988,17 +4898,14 @@
       <c r="Q12" s="30"/>
       <c r="R12" s="24"/>
       <c r="S12" s="30"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="36"/>
-      <c r="V12" s="36"/>
+      <c r="T12" s="30"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
       <c r="W12" s="30"/>
       <c r="X12" s="30"/>
       <c r="Y12" s="30"/>
-      <c r="Z12" s="30"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="30"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="25"/>
       <c r="B13" s="32"/>
       <c r="C13" s="34"/>
@@ -5020,17 +4927,14 @@
       <c r="Q13" s="30"/>
       <c r="R13" s="24"/>
       <c r="S13" s="30"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="36"/>
-      <c r="V13" s="36"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
       <c r="W13" s="30"/>
       <c r="X13" s="30"/>
       <c r="Y13" s="30"/>
-      <c r="Z13" s="30"/>
-      <c r="AA13" s="30"/>
-      <c r="AB13" s="30"/>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="25"/>
       <c r="B14" s="32"/>
       <c r="C14" s="34"/>
@@ -5050,17 +4954,14 @@
       <c r="Q14" s="30"/>
       <c r="R14" s="24"/>
       <c r="S14" s="30"/>
-      <c r="T14" s="36"/>
-      <c r="U14" s="36"/>
-      <c r="V14" s="36"/>
+      <c r="T14" s="30"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="30"/>
       <c r="W14" s="30"/>
       <c r="X14" s="30"/>
       <c r="Y14" s="30"/>
-      <c r="Z14" s="30"/>
-      <c r="AA14" s="30"/>
-      <c r="AB14" s="30"/>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="25"/>
       <c r="B15" s="32"/>
       <c r="C15" s="34"/>
@@ -5080,17 +4981,14 @@
       <c r="Q15" s="30"/>
       <c r="R15" s="24"/>
       <c r="S15" s="30"/>
-      <c r="T15" s="36"/>
-      <c r="U15" s="36"/>
-      <c r="V15" s="36"/>
+      <c r="T15" s="30"/>
+      <c r="U15" s="30"/>
+      <c r="V15" s="30"/>
       <c r="W15" s="30"/>
       <c r="X15" s="30"/>
       <c r="Y15" s="30"/>
-      <c r="Z15" s="30"/>
-      <c r="AA15" s="30"/>
-      <c r="AB15" s="30"/>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="25"/>
       <c r="B16" s="25"/>
       <c r="C16" s="34"/>
@@ -5110,15 +5008,12 @@
       <c r="Q16" s="30"/>
       <c r="R16" s="24"/>
       <c r="S16" s="30"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="36"/>
-      <c r="V16" s="36"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
       <c r="W16" s="30"/>
       <c r="X16" s="30"/>
       <c r="Y16" s="30"/>
-      <c r="Z16" s="30"/>
-      <c r="AA16" s="30"/>
-      <c r="AB16" s="30"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Data/DataTable/01_Character_Table_fix.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F1BC96-E3C4-4EB6-97BB-C8C9ABED0A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D17337-80E8-43E9-A676-3AD04E59A324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -635,6 +635,141 @@
         </r>
       </text>
     </comment>
+    <comment ref="R3" authorId="0" shapeId="0" xr:uid="{E1B47B87-AFB7-4700-B0FF-BC6D52144777}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">물리
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">화염
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">3: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">방사능
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">4: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">중력
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">5: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">공허
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">6: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>신성</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="S3" authorId="0" shapeId="0" xr:uid="{8FE4A925-8291-466B-98E1-E41BD960CA85}">
       <text>
         <r>
@@ -775,7 +910,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="138">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1287,6 +1422,14 @@
   </si>
   <si>
     <t>penguin_Rifleman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.0,1.0,1.0,1.0,1.0,1.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,0.3,0.3,0.3,0.3,0.3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1294,10 +1437,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0.0_);[Red]\(0.0\)"/>
     <numFmt numFmtId="178" formatCode="00"/>
+    <numFmt numFmtId="184" formatCode="0.0000000_);[Red]\(0.0000000\)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1453,7 +1597,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1560,6 +1704,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4235,7 +4385,7 @@
     <col min="15" max="15" width="21.125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="28" style="33" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.125" style="37" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18.5" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="21" bestFit="1" customWidth="1"/>
   </cols>
@@ -4248,6 +4398,7 @@
       <c r="C1"/>
       <c r="D1"/>
       <c r="P1"/>
+      <c r="R1"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
@@ -4369,7 +4520,7 @@
         <v>97</v>
       </c>
       <c r="R3" s="29" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="S3" s="29" t="s">
         <v>97</v>
@@ -4501,10 +4652,10 @@
         <v>134</v>
       </c>
       <c r="Q5" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="R5" s="31">
-        <v>1</v>
+        <v>136</v>
+      </c>
+      <c r="R5" s="36" t="s">
+        <v>137</v>
       </c>
       <c r="S5" s="30" t="s">
         <v>105</v>
@@ -4566,9 +4717,15 @@
         <v>1.3</v>
       </c>
       <c r="P6" s="25"/>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="30"/>
+      <c r="Q6" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="R6" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="S6" s="30" t="s">
+        <v>105</v>
+      </c>
       <c r="T6" s="25" t="s">
         <v>107</v>
       </c>
@@ -4626,9 +4783,15 @@
         <v>1.3</v>
       </c>
       <c r="P7" s="25"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="30"/>
+      <c r="Q7" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="R7" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>105</v>
+      </c>
       <c r="T7" s="30" t="s">
         <v>108</v>
       </c>
@@ -4686,9 +4849,15 @@
         <v>1</v>
       </c>
       <c r="P8" s="25"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="30"/>
+      <c r="Q8" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="R8" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="S8" s="30" t="s">
+        <v>105</v>
+      </c>
       <c r="T8" s="30" t="s">
         <v>135</v>
       </c>
@@ -4746,9 +4915,15 @@
         <v>1</v>
       </c>
       <c r="P9" s="25"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="30"/>
+      <c r="Q9" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="R9" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>105</v>
+      </c>
       <c r="T9" s="30" t="s">
         <v>109</v>
       </c>
@@ -4806,9 +4981,15 @@
         <v>1</v>
       </c>
       <c r="P10" s="25"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="30"/>
+      <c r="Q10" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="R10" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="S10" s="30" t="s">
+        <v>105</v>
+      </c>
       <c r="T10" s="30" t="s">
         <v>110</v>
       </c>
@@ -4866,9 +5047,15 @@
         <v>1</v>
       </c>
       <c r="P11" s="25"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="30"/>
+      <c r="Q11" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="R11" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="S11" s="30" t="s">
+        <v>105</v>
+      </c>
       <c r="T11" s="30" t="s">
         <v>111</v>
       </c>
@@ -4896,7 +5083,7 @@
       <c r="O12" s="31"/>
       <c r="P12" s="25"/>
       <c r="Q12" s="30"/>
-      <c r="R12" s="24"/>
+      <c r="R12" s="36"/>
       <c r="S12" s="30"/>
       <c r="T12" s="30"/>
       <c r="U12" s="30"/>
@@ -4925,7 +5112,7 @@
       <c r="O13" s="31"/>
       <c r="P13" s="25"/>
       <c r="Q13" s="30"/>
-      <c r="R13" s="24"/>
+      <c r="R13" s="36"/>
       <c r="S13" s="30"/>
       <c r="T13" s="30"/>
       <c r="U13" s="30"/>
@@ -4952,7 +5139,7 @@
       <c r="O14" s="31"/>
       <c r="P14" s="25"/>
       <c r="Q14" s="30"/>
-      <c r="R14" s="24"/>
+      <c r="R14" s="36"/>
       <c r="S14" s="30"/>
       <c r="T14" s="30"/>
       <c r="U14" s="30"/>
@@ -4979,7 +5166,7 @@
       <c r="O15" s="31"/>
       <c r="P15" s="25"/>
       <c r="Q15" s="30"/>
-      <c r="R15" s="24"/>
+      <c r="R15" s="36"/>
       <c r="S15" s="30"/>
       <c r="T15" s="30"/>
       <c r="U15" s="30"/>
@@ -5006,7 +5193,7 @@
       <c r="O16" s="31"/>
       <c r="P16" s="25"/>
       <c r="Q16" s="30"/>
-      <c r="R16" s="24"/>
+      <c r="R16" s="36"/>
       <c r="S16" s="30"/>
       <c r="T16" s="30"/>
       <c r="U16" s="30"/>
@@ -5022,7 +5209,7 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D44D287-4A0D-4E30-B02E-F978C229F037}">
           <x14:formula1>
             <xm:f>'!Logic'!$A$5:$A$19</xm:f>
